--- a/docs/files/exports/combined-combined-client-proposal.xlsx
+++ b/docs/files/exports/combined-combined-client-proposal.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1,678 words</t>
+          <t>1,389 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Combined Web + App Client Proposal  Full-stack client proposal covering both website and mobile application scope, pricing, and deliverables.  Scope: This document covers both Website / Web Application and Mobile Applic...</t>
+          <t xml:space="preserve"> Combined Web + App Client Proposal  Full-stack client proposal covering Website and Mobile Application scope, pricing, deliverables, and terms in a single document.  Covers: Website / Web Application Projects | Mobile A...</t>
         </is>
       </c>
     </row>
